--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/may-2026.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/may-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC may-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC may-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">

--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/may-2026.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/may-2026.xlsx
@@ -788,7 +788,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>DIRECCION DE SANIDAD DE LA ARMADA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>NETSUS SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ASOCIACION DE MUNICIPIOS METROPOLITANOS PARA LA SE</t>
+          <t>ASOCIACION DE MUNICIPIOS METROPOLITANOS PARA LA SEGURIDAD CIUDADANA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>COMISION CHILENA DE ENERGIA NUCLEAR</t>
+          <t>Comisión Chilena de Energía Nuclear</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Departamento de Salud</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Subsecretaria de Transportes</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Curanilahue - Salud</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>NETSUS SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Subsecretaria de Transportes</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Subsecretaria de Transportes</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>NETSUS SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>NETSUS SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">

--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/may-2026.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/may-2026.xlsx
@@ -562,7 +562,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +818,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +944,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1009,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1074,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1139,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1204,11 @@
           <t>76.288.338-4</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1330,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1395,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1460,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1525,11 @@
           <t>76.981.642-9</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1590,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1655,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1720,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1846,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1911,11 @@
           <t>92.580.000-7</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1976,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2041,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2106,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2171,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2236,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2301,11 @@
           <t>76.288.338-4</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2366,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2431,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2496,11 @@
           <t>76.981.642-9</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2561,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2626,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2752,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2817,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2882,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2947,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3012,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3077,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3203,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3268,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3333,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3398,11 @@
           <t>76.288.338-4</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3463,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3589,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3654,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3719,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3784,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3910,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3975,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4040,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4166,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4292,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4357,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4422,11 @@
           <t>76.334.381-2</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4487,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4552,11 @@
           <t>76.288.338-4</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4617,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/may-2026.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/may-2026.xlsx
@@ -3821,7 +3821,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
